--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487913_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487913_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.838</v>
+        <v>8.2159</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1254</v>
+        <v>7.2978</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7126</v>
+        <v>0.9181</v>
       </c>
       <c r="G2" t="n">
         <v>2.666</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1618</v>
+        <v>0.5397</v>
       </c>
       <c r="T2" t="n">
-        <v>0.503</v>
+        <v>0.6754</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3412</v>
+        <v>-0.1357</v>
       </c>
       <c r="V2" t="n">
         <v>3.9696</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1871</v>
+        <v>4.0331</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6267</v>
+        <v>3.4831</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5604</v>
+        <v>0.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3821</v>
+        <v>1.5868</v>
       </c>
       <c r="H3" t="n">
-        <v>3.277</v>
+        <v>0.2111</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8949</v>
+        <v>1.3757</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3254</v>
+        <v>2.2646</v>
       </c>
       <c r="K3" t="n">
-        <v>4.155</v>
+        <v>0.893</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.8296</v>
+        <v>1.3716</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9433</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.878</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0653</v>
+        <v>0.0041</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8325</v>
+        <v>3.1218</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0812</v>
+        <v>3.3299</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7532</v>
+        <v>0.6089</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4626</v>
+        <v>0.2591</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2906</v>
+        <v>0.3498</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2193</v>
+        <v>-1.2843</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0874</v>
+        <v>1.1675</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.868</v>
+        <v>-2.4518</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0891</v>
+        <v>3.8606</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2455</v>
+        <v>3.858</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8436</v>
+        <v>0.0026</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5868</v>
+        <v>1.3821</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2111</v>
+        <v>3.277</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3757</v>
+        <v>-1.8949</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2646</v>
+        <v>2.3254</v>
       </c>
       <c r="K4" t="n">
-        <v>0.893</v>
+        <v>4.155</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3716</v>
+        <v>-1.8296</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.9433</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.878</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0041</v>
+        <v>-0.0653</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1218</v>
+        <v>0.8325</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3299</v>
+        <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6647999999999999</v>
+        <v>1.4267</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0215</v>
+        <v>0.6939</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6433</v>
+        <v>0.7327</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2843</v>
+        <v>0.2193</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1675</v>
+        <v>2.0874</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4518</v>
+        <v>-1.868</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9499</v>
+        <v>3.5296</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8291</v>
+        <v>3.1739</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1208</v>
+        <v>0.3557</v>
       </c>
       <c r="G5" t="n">
         <v>1.2391</v>
@@ -844,13 +844,13 @@
         <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0268</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.171</v>
+        <v>0.1738</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1442</v>
+        <v>0.3791</v>
       </c>
       <c r="V5" t="n">
         <v>0.697</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2771</v>
+        <v>2.1885</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8707</v>
+        <v>3.4298</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5937</v>
+        <v>-1.2413</v>
       </c>
       <c r="G6" t="n">
         <v>2.8542</v>
@@ -922,13 +922,13 @@
         <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7933</v>
+        <v>0.1181</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8482</v>
+        <v>-0.2891</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0548</v>
+        <v>0.4071</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4081</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1884</v>
+        <v>0.6373</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.59</v>
+        <v>-0.8819</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4017</v>
+        <v>1.5191</v>
       </c>
       <c r="G7" t="n">
         <v>1.7835</v>
@@ -1000,13 +1000,13 @@
         <v>2.7055</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1176</v>
+        <v>-0.2919</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6277</v>
+        <v>0.0805</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4899</v>
+        <v>-0.3725</v>
       </c>
       <c r="V7" t="n">
         <v>-0.23</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0472</v>
+        <v>-0.2723</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.534</v>
+        <v>-2.0821</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4868</v>
+        <v>1.8098</v>
       </c>
       <c r="G8" t="n">
         <v>0.1914</v>
@@ -1078,13 +1078,13 @@
         <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5924</v>
+        <v>0.1825</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2362</v>
+        <v>0.2158</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3562</v>
+        <v>-0.0332</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6445</v>
+        <v>-1.8229</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5175</v>
+        <v>-1.6666</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.127</v>
+        <v>-0.1564</v>
       </c>
       <c r="G9" t="n">
         <v>-3.6533</v>
@@ -1156,13 +1156,13 @@
         <v>1.8731</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1357</v>
+        <v>-0.0427</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4129</v>
+        <v>0.2639</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2772</v>
+        <v>-0.3066</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1489</v>
+        <v>-3.0789</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6136</v>
+        <v>-2.1913</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5354</v>
+        <v>-0.8877</v>
       </c>
       <c r="G10" t="n">
         <v>-0.824</v>
@@ -1234,13 +1234,13 @@
         <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5482</v>
+        <v>0.6182</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2049</v>
+        <v>0.6272</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3432</v>
+        <v>-0.0091</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5838</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>16.3122</v>
+        <v>17.2909</v>
       </c>
       <c r="E11" t="n">
-        <v>13.4423</v>
+        <v>14.4207</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8698</v>
+        <v>2.8699</v>
       </c>
       <c r="G11" t="n">
         <v>7.2258</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6945</v>
+        <v>1.694499999999999</v>
       </c>
       <c r="I11" t="n">
         <v>5.5313</v>
@@ -1312,10 +1312,10 @@
         <v>18.7307</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7336</v>
+        <v>3.7124</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7218</v>
+        <v>2.7005</v>
       </c>
       <c r="U11" t="n">
         <v>1.0116</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.3912</v>
+        <v>8.490500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>7.3643</v>
+        <v>7.4715</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0269</v>
+        <v>1.019</v>
       </c>
       <c r="G12" t="n">
         <v>5.5872</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1148</v>
+        <v>-0.0155</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4319</v>
+        <v>-0.3248</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3171</v>
+        <v>0.3093</v>
       </c>
       <c r="V12" t="n">
         <v>2.9188</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0603</v>
+        <v>3.554</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0849</v>
+        <v>2.9777</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0246</v>
+        <v>0.5763</v>
       </c>
       <c r="G13" t="n">
         <v>5.2779</v>
@@ -1468,13 +1468,13 @@
         <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4091</v>
+        <v>0.0847</v>
       </c>
       <c r="T13" t="n">
-        <v>0.152</v>
+        <v>0.0448</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5610000000000001</v>
+        <v>0.0398</v>
       </c>
       <c r="V13" t="n">
         <v>1.5213</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SIENCHE GUEMETA</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.867</v>
+        <v>0.2661</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1303</v>
+        <v>0.6428</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2633</v>
+        <v>-0.3767</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08</v>
+        <v>-0.8381</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3519</v>
+        <v>0.6143</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2719</v>
+        <v>-1.4524</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0313</v>
+        <v>1.1337</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1277</v>
+        <v>1.0554</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0963</v>
+        <v>0.0784</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9513</v>
+        <v>-1.9719</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7758</v>
+        <v>-0.4411</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1755</v>
+        <v>-1.5308</v>
       </c>
       <c r="P14" t="n">
+        <v>1.2487</v>
+      </c>
+      <c r="Q14" t="n">
         <v>-0.2081</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-1.0406</v>
-      </c>
       <c r="R14" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1013</v>
+        <v>-0.1445</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5558</v>
+        <v>-0.2829</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5455</v>
+        <v>0.1383</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1061</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>J. SIENCHE GUEMETA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1244</v>
+        <v>0.2481</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8571</v>
+        <v>0.8089</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9815</v>
+        <v>-0.5608</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8381</v>
+        <v>0.08</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6143</v>
+        <v>0.3519</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4524</v>
+        <v>-0.2719</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1337</v>
+        <v>1.0313</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0554</v>
+        <v>1.1277</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0784</v>
+        <v>-0.0963</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9719</v>
+        <v>-0.9513</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4411</v>
+        <v>-0.7758</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5308</v>
+        <v>-0.1755</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.535</v>
+        <v>0.4823</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.2343</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4664</v>
+        <v>0.248</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.1061</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9794</v>
+        <v>-0.5278</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0278</v>
+        <v>1.1349</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0072</v>
+        <v>-1.6627</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7054</v>
@@ -1702,13 +1702,13 @@
         <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.1336</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1586</v>
+        <v>-0.0514</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4266</v>
+        <v>-0.0822</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9376</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>J. BLACK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.6461</v>
+        <v>-2.5082</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.6286</v>
+        <v>-1.8404</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0174</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.169</v>
+        <v>-2.7074</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8189</v>
+        <v>-0.3218</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6499</v>
+        <v>-2.3856</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7363</v>
+        <v>-0.315</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8147</v>
+        <v>1.0745</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0784</v>
+        <v>-1.3896</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5674</v>
+        <v>-2.3924</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0041</v>
+        <v>-1.3963</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5715</v>
+        <v>-0.996</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.3299</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.3705</v>
+        <v>-1.2487</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4366</v>
+        <v>-0.1546</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3106</v>
+        <v>-0.2767</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1259</v>
+        <v>0.122</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5838</v>
+        <v>0.3538</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7513</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BLACK</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.0504</v>
+        <v>-3.4001</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.269</v>
+        <v>-3.3787</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7813</v>
+        <v>-0.0213</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.7074</v>
+        <v>-0.169</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3218</v>
+        <v>-0.8189</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.3856</v>
+        <v>0.6499</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.315</v>
+        <v>-0.7363</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0745</v>
+        <v>-0.8147</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3896</v>
+        <v>0.0784</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3924</v>
+        <v>0.5674</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3963</v>
+        <v>-0.0041</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.996</v>
+        <v>0.5715</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-3.3299</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.2487</v>
+        <v>-4.3705</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6968</v>
+        <v>0.6826</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7053</v>
+        <v>0.5606</v>
       </c>
       <c r="U18" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3538</v>
+        <v>-0.5838</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3538</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.4493</v>
+        <v>-4.1176</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6047</v>
+        <v>-2.3904</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8447</v>
+        <v>-1.7272</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6212</v>
@@ -1936,13 +1936,13 @@
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0907</v>
+        <v>0.4224</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1553</v>
+        <v>0.3696</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0646</v>
+        <v>0.0529</v>
       </c>
       <c r="V19" t="n">
         <v>-2.3351</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9065</v>
+        <v>-4.2851</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9048</v>
+        <v>-1.6905</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0017</v>
+        <v>-2.5946</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4049</v>
@@ -2014,13 +2014,13 @@
         <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2311</v>
+        <v>-0.6097</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6929</v>
+        <v>-0.4786</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5382</v>
+        <v>-0.1311</v>
       </c>
       <c r="V20" t="n">
         <v>-0.23</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6695</v>
+        <v>-5.3456</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0906</v>
+        <v>-3.3008</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5789</v>
+        <v>-2.0447</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8531</v>
+        <v>-4.8719</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.5803</v>
+        <v>-2.0275</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2728</v>
+        <v>-2.8444</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2485</v>
+        <v>-1.6588</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3268</v>
+        <v>-0.3778</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0784</v>
+        <v>-1.281</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6046</v>
+        <v>-3.2131</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2535</v>
+        <v>-1.6497</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3512</v>
+        <v>-1.5634</v>
       </c>
       <c r="P21" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1618</v>
+        <v>-0.4924</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0091</v>
+        <v>-0.6014</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1527</v>
+        <v>0.109</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9376</v>
+        <v>-0.8137</v>
       </c>
       <c r="W21" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1675</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.8051</v>
+        <v>-5.829</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8366</v>
+        <v>-3.3049</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9686</v>
+        <v>-2.5241</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.8719</v>
+        <v>-3.8531</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0275</v>
+        <v>-2.5803</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8444</v>
+        <v>-1.2728</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6588</v>
+        <v>-1.2485</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3778</v>
+        <v>-1.3268</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.281</v>
+        <v>0.0784</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.2131</v>
+        <v>-2.6046</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6497</v>
+        <v>-1.2535</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5634</v>
+        <v>-1.3512</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8325</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.952</v>
+        <v>0.0023</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1372</v>
+        <v>-0.2052</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8148</v>
+        <v>0.2075</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8137</v>
+        <v>-0.9376</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8137</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-16.3122</v>
+        <v>-13.4547</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.869899999999996</v>
+        <v>-2.8699</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.4423</v>
+        <v>-10.5846</v>
       </c>
       <c r="G23" t="n">
         <v>-7.2259</v>
@@ -2221,19 +2221,19 @@
         <v>-5.531299999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>7.655999999999998</v>
+        <v>7.655999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>6.798799999999999</v>
+        <v>6.798799999999998</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8571999999999986</v>
+        <v>0.8571999999999989</v>
       </c>
       <c r="M23" t="n">
         <v>-14.8817</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.493399999999999</v>
+        <v>-8.493400000000001</v>
       </c>
       <c r="O23" t="n">
         <v>-6.388399999999999</v>
@@ -2248,16 +2248,16 @@
         <v>13.5277</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.7336</v>
+        <v>0.124</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0116</v>
+        <v>-1.0117</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.7219</v>
+        <v>1.1355</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.149999999999999</v>
+        <v>-1.15</v>
       </c>
       <c r="W23" t="n">
         <v>9.2164</v>
